--- a/output/graficos_regionales/plot_regional_serie_i_ingr_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_a_2020_arica_y_parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:40</t>
+    <t xml:space="preserve">2026-10-05 02:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -470,7 +470,7 @@
         <v>752070.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>812081.12</v>
+        <v>812081.13</v>
       </c>
     </row>
     <row r="3">
@@ -522,10 +522,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1099959.12</v>
+        <v>1099959.13</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1190492.62</v>
+        <v>1190492.63</v>
       </c>
     </row>
     <row r="8">
